--- a/tools/importer/reports/import-product.report.xlsx
+++ b/tools/importer/reports/import-product.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,6 +19,9 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>links</t>
+  </si>
+  <si>
     <t>path</t>
   </si>
   <si>
@@ -37,6 +40,48 @@
     <t>url</t>
   </si>
   <si>
+    <t>nav.report.json</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>["Contact your Representative"]</t>
+  </si>
+  <si>
+    <t>nav</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>2026-10-05T10:32:51.268Z</t>
+  </si>
+  <si>
+    <t>https://www.lupin.com/US/product</t>
+  </si>
+  <si>
+    <t>us/contact-us.report.json</t>
+  </si>
+  <si>
+    <t>["hero-map","cards-location","form-contact","columns-contacts"]</t>
+  </si>
+  <si>
+    <t>us/contact-us</t>
+  </si>
+  <si>
+    <t>contact-us</t>
+  </si>
+  <si>
+    <t>2026-10-05T14:54:53.678Z</t>
+  </si>
+  <si>
+    <t>Contact Lupin US | Get in Touch with Our Team</t>
+  </si>
+  <si>
+    <t>https://www.lupin.com/US/contact-us</t>
+  </si>
+  <si>
     <t>us/product.report.json</t>
   </si>
   <si>
@@ -46,19 +91,13 @@
     <t>us/product</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>product</t>
   </si>
   <si>
-    <t>2026-10-05T10:28:00.088Z</t>
+    <t>2026-10-05T14:55:04.507Z</t>
   </si>
   <si>
     <t>Explore Our Products | Quality Medicines for Better Health.</t>
-  </si>
-  <si>
-    <t>https://www.lupin.com/US/product</t>
   </si>
 </sst>
 </file>
@@ -447,19 +486,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="9" max="9" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,35 +524,99 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
       </c>
       <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-product.report.xlsx
+++ b/tools/importer/reports/import-product.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
   <si>
     <t>_reportFile</t>
   </si>
@@ -73,7 +73,7 @@
     <t>contact-us</t>
   </si>
   <si>
-    <t>2026-10-05T14:54:53.678Z</t>
+    <t>2026-10-05T14:56:25.891Z</t>
   </si>
   <si>
     <t>Contact Lupin US | Get in Touch with Our Team</t>
@@ -82,22 +82,52 @@
     <t>https://www.lupin.com/US/contact-us</t>
   </si>
   <si>
+    <t>us/hcpportal.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","cards-product","cards-link-tile","cards-link-tile"]</t>
+  </si>
+  <si>
+    <t>us/hcpportal</t>
+  </si>
+  <si>
+    <t>product</t>
+  </si>
+  <si>
+    <t>2026-10-05T18:14:40.021Z</t>
+  </si>
+  <si>
+    <t>Explore Our Products | Quality Medicines for Better Health.</t>
+  </si>
+  <si>
     <t>us/product.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","cards-product","cards-link-tile","cards-link-tile"]</t>
-  </si>
-  <si>
     <t>us/product</t>
   </si>
   <si>
-    <t>product</t>
-  </si>
-  <si>
     <t>2026-10-05T14:55:04.507Z</t>
   </si>
   <si>
-    <t>Explore Our Products | Quality Medicines for Better Health.</t>
+    <t>us/product/glycerol-phenylbutyrate-oral-liquid.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-product-detail","tabs-audience","columns-anchor-nav","columns-anchor-nav","hero-green-panel","hero-green-panel","columns-icon-tips","cards-pharmacy","cards-pharmacy","accordion-faq","accordion-faq","columns-cta-banner","columns-cta-banner"]</t>
+  </si>
+  <si>
+    <t>us/product/glycerol-phenylbutyrate-oral-liquid</t>
+  </si>
+  <si>
+    <t>product-detail</t>
+  </si>
+  <si>
+    <t>2026-10-05T17:10:00.610Z</t>
+  </si>
+  <si>
+    <t>Glycerol Phenylbutyrate Oral Liquid</t>
+  </si>
+  <si>
+    <t>https://www.lupin.com/US/product/glycerol-phenylbutyrate-oral-liquid</t>
   </si>
 </sst>
 </file>
@@ -486,17 +516,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="1" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="4" max="4" width="48" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
-    <col min="9" max="9" width="37" customWidth="1"/>
+    <col min="8" max="9" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -613,6 +641,64 @@
       </c>
       <c r="I4" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
